--- a/HardwareSemis.xlsx
+++ b/HardwareSemis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341140F6-4B7D-4A25-9110-5D6D7D691DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BD0EA4-CFBF-4672-A917-801FFD9720AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="2750" windowWidth="19980" windowHeight="16070" xr2:uid="{98D8347A-DFA4-427C-8784-96E5573B433C}"/>
+    <workbookView xWindow="13160" yWindow="4450" windowWidth="21120" windowHeight="11660" xr2:uid="{98D8347A-DFA4-427C-8784-96E5573B433C}"/>
   </bookViews>
   <sheets>
     <sheet name="Semiconductors" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,15 @@
     <externalReference r:id="rId22"/>
     <externalReference r:id="rId23"/>
     <externalReference r:id="rId24"/>
+    <externalReference r:id="rId25"/>
+    <externalReference r:id="rId26"/>
   </externalReferences>
   <definedNames>
     <definedName name="CNY">FX!$B$4</definedName>
     <definedName name="JPY">FX!$C$6</definedName>
     <definedName name="KRW">FX!$C$3</definedName>
     <definedName name="None">FX!$B$4</definedName>
+    <definedName name="NTD">FX!$C$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="282">
   <si>
     <t>Name</t>
   </si>
@@ -852,9 +855,6 @@
     <t>EPS</t>
   </si>
   <si>
-    <t>P/E</t>
-  </si>
-  <si>
     <t>Silicon Spin Qubits</t>
   </si>
   <si>
@@ -880,6 +880,63 @@
   </si>
   <si>
     <t>JPY</t>
+  </si>
+  <si>
+    <t>Fremont</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>INFQ</t>
+  </si>
+  <si>
+    <t>Infeqtion</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Sandisk</t>
+  </si>
+  <si>
+    <t>SNDK</t>
+  </si>
+  <si>
+    <t>EV/E</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>CEO Salary</t>
+  </si>
+  <si>
+    <t>CTO Salary</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>Coherent</t>
+  </si>
+  <si>
+    <t>COHR</t>
   </si>
 </sst>
 </file>
@@ -929,7 +986,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -937,12 +994,67 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -976,8 +1088,21 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1051,18 +1176,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="M3">
-            <v>640</v>
+          <cell r="K3">
+            <v>907.57171200000005</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="M5">
-            <v>1670</v>
+          <cell r="K5">
+            <v>9090</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="M6">
-            <v>2174</v>
+          <cell r="K6">
+            <v>7937</v>
           </cell>
         </row>
       </sheetData>
@@ -1085,18 +1210,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="J3">
-            <v>135.42215899999999</v>
+          <cell r="M3">
+            <v>640</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>1646.404</v>
+          <cell r="M5">
+            <v>1670</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>1199.432</v>
+          <cell r="M6">
+            <v>2174</v>
           </cell>
         </row>
       </sheetData>
@@ -1119,17 +1244,17 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="K3">
-            <v>811.04812700000002</v>
+          <cell r="L3">
+            <v>148.08975799999999</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>1203</v>
+          <cell r="L5">
+            <v>3735</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
+          <cell r="L6">
             <v>0</v>
           </cell>
         </row>
@@ -1154,17 +1279,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>63.864503999999997</v>
+            <v>135.42215899999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>522.64</v>
+            <v>1646.404</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>227.42599999999999</v>
+            <v>1199.432</v>
           </cell>
         </row>
       </sheetData>
@@ -1183,6 +1308,74 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="K3">
+            <v>811.04812700000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>1203</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="J3">
+            <v>63.864503999999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>522.64</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>227.42599999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
       <sheetName val="Presentation"/>
       <sheetName val="Papers"/>
       <sheetName val="Glossary"/>
@@ -1191,12 +1384,12 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>354.27959099999998</v>
+            <v>368.98291699999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>1657</v>
+            <v>3336.799</v>
           </cell>
         </row>
         <row r="6">
@@ -1214,7 +1407,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1256,7 +1449,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1292,7 +1485,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1339,74 +1532,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="K3">
-            <v>6758.9192499999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>112651.8</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>19330.2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>115.959118</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>423.3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>796.7</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1426,17 +1551,85 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>4860</v>
+            <v>4888</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>10718</v>
+            <v>14174</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>64229</v>
+            <v>66057</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="K3">
+            <v>6758.9192499999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>112651.8</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>19330.2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>115.959118</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>423.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>796.7</v>
           </cell>
         </row>
       </sheetData>
@@ -1527,18 +1720,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="M3">
-            <v>1641</v>
+          <cell r="J3">
+            <v>1108.841326</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="M5">
-            <v>7243</v>
+          <cell r="J5">
+            <v>9154</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="M6">
-            <v>3220</v>
+          <cell r="J6">
+            <v>13258</v>
           </cell>
         </row>
       </sheetData>
@@ -1561,18 +1754,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="L3">
-            <v>1114</v>
+          <cell r="M3">
+            <v>1641</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="L5">
-            <v>13032</v>
+          <cell r="M5">
+            <v>7243</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="L6">
-            <v>14554</v>
+          <cell r="M6">
+            <v>3220</v>
           </cell>
         </row>
       </sheetData>
@@ -1596,17 +1789,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="K3">
-            <v>907.57171200000005</v>
+            <v>799</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>9090</v>
+            <v>13479</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>7937</v>
+            <v>6553</v>
           </cell>
         </row>
       </sheetData>
@@ -1669,18 +1862,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="J3">
-            <v>1108.841326</v>
+          <cell r="L3">
+            <v>1114</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>9154</v>
+          <cell r="L5">
+            <v>13032</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>13258</v>
+          <cell r="L6">
+            <v>14554</v>
           </cell>
         </row>
       </sheetData>
@@ -1987,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B77F9E42-3F4A-4F5B-8F7C-4C05A85AC67E}">
-  <dimension ref="A1:U54"/>
+  <dimension ref="A2:AA58"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.453125" customWidth="1"/>
@@ -1997,204 +2190,216 @@
     <col min="5" max="7" width="9.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.1796875" style="3"/>
     <col min="10" max="10" width="11.81640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.453125" style="18" customWidth="1"/>
+    <col min="13" max="15" width="7.453125" customWidth="1"/>
+    <col min="16" max="16" width="7.453125" style="19" customWidth="1"/>
+    <col min="17" max="17" width="7.90625" style="18" customWidth="1"/>
+    <col min="18" max="21" width="7.90625" customWidth="1"/>
+    <col min="22" max="22" width="7.90625" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="L1" s="18" t="s">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>272</v>
+      </c>
+      <c r="M2" s="21">
+        <f>AVERAGE(M5:M19)</f>
+        <v>31.284158119831861</v>
+      </c>
+      <c r="N2" s="21">
+        <f>AVERAGE(N5:N19)</f>
+        <v>21.202967297362857</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="L3" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="25"/>
+      <c r="Z3" s="13">
+        <f>AVERAGE(Z5:Z35)</f>
+        <v>1108057.2676866585</v>
+      </c>
+      <c r="AA3" s="13">
+        <f>AVERAGE(AA5:AA35)</f>
+        <v>772594.93333333335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="L2">
+      <c r="L4" s="18">
         <v>2025</v>
       </c>
-      <c r="M2">
+      <c r="M4">
         <v>2026</v>
       </c>
-      <c r="N2">
-        <f>+M2+1</f>
+      <c r="N4">
+        <f>+M4+1</f>
         <v>2027</v>
       </c>
-      <c r="O2">
-        <f>+N2+1</f>
+      <c r="O4">
+        <f>+N4+1</f>
         <v>2028</v>
       </c>
-      <c r="P2">
-        <f>+O2+1</f>
+      <c r="P4" s="19">
+        <f>+O4+1</f>
         <v>2029</v>
       </c>
-      <c r="Q2">
+      <c r="Q4" s="17">
+        <v>2024</v>
+      </c>
+      <c r="R4">
         <v>2025</v>
       </c>
-      <c r="R2">
+      <c r="S4">
         <v>2026</v>
       </c>
-      <c r="S2">
-        <f>+R2+1</f>
+      <c r="T4">
+        <f>+S4+1</f>
         <v>2027</v>
       </c>
-      <c r="T2">
-        <f>+S2+1</f>
+      <c r="U4">
+        <f>+T4+1</f>
         <v>2028</v>
       </c>
-      <c r="U2">
-        <f>+T2+1</f>
+      <c r="V4" s="19">
+        <f>+U4+1</f>
         <v>2029</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="W4" t="s">
+        <v>278</v>
+      </c>
+      <c r="X4" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>274</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4">
-        <v>194</v>
-      </c>
-      <c r="E3" s="6">
-        <f>+D3*H3</f>
-        <v>4714200</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="D5" s="4">
+        <v>199.6</v>
+      </c>
+      <c r="E5" s="6">
+        <f>+D5*H5</f>
+        <v>4850280</v>
+      </c>
+      <c r="F5" s="6">
         <f>+[1]Main!$K$5-[1]Main!$K$6</f>
         <v>48325</v>
       </c>
-      <c r="G3" s="6">
-        <f>+E3-F3</f>
-        <v>4665875</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="G5" s="6">
+        <f>+E5-F5</f>
+        <v>4801955</v>
+      </c>
+      <c r="H5" s="6">
         <f>+[1]Main!$K$3</f>
         <v>24300</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="J3" s="10">
-        <v>45805</v>
-      </c>
-      <c r="K3">
+      <c r="I5" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J5" s="10">
+        <v>46101</v>
+      </c>
+      <c r="K5">
         <v>1993</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="4">
-        <v>344</v>
-      </c>
-      <c r="E4" s="6">
-        <f>+D4*H4</f>
-        <v>1671840</v>
-      </c>
-      <c r="F4" s="6">
-        <f>+[2]Main!$J$5-[2]Main!$J$6</f>
-        <v>-53511</v>
-      </c>
-      <c r="G4" s="6">
-        <f>+E4-F4</f>
-        <v>1725351</v>
-      </c>
-      <c r="H4" s="6">
-        <f>+[2]Main!$J$3</f>
-        <v>4860</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J4" s="10">
-        <v>45722</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="4">
-        <v>300.29000000000002</v>
-      </c>
-      <c r="E5" s="6">
-        <f>+D5*H5/5</f>
-        <v>1557363.9980000001</v>
-      </c>
-      <c r="F5" s="6">
-        <f>([3]Main!$J$7-[3]Main!$J$8)/FX!C5</f>
-        <v>-87849.921703726897</v>
-      </c>
-      <c r="G5" s="6">
-        <f>+E5-F5</f>
-        <v>1645213.9197037271</v>
-      </c>
-      <c r="H5" s="6">
-        <f>+[3]Main!$J$4</f>
-        <v>25931</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J5" s="10">
-        <v>45652</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="L5" s="20">
+        <f>($G5/$H5)/R5</f>
+        <v>67.214733630077546</v>
+      </c>
+      <c r="M5" s="21">
+        <f>($G$5/$H$5)/S5</f>
+        <v>40.328840178046526</v>
+      </c>
+      <c r="N5" s="21">
+        <f>($G$5/$H$5)/T5</f>
+        <v>23.866101071549274</v>
+      </c>
+      <c r="O5" s="21">
+        <f>($G$5/$H$5)/U5</f>
+        <v>17.754835298511047</v>
+      </c>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="22">
+        <v>1.19</v>
+      </c>
+      <c r="R5" s="2">
+        <v>2.94</v>
+      </c>
+      <c r="S5" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="T5" s="2">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="U5" s="2">
+        <v>11.13</v>
+      </c>
+      <c r="Z5" s="13">
+        <v>1486199</v>
+      </c>
+      <c r="AA5" s="13">
+        <v>844087</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>46</v>
       </c>
@@ -2202,955 +2407,1326 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D6" s="4">
-        <v>1440</v>
+        <v>440.61</v>
       </c>
       <c r="E6" s="6">
-        <f>+D6*H6/FX!C2</f>
-        <v>1142614.4430844553</v>
+        <f>+D6*H6/5</f>
+        <v>2285091.5819999999</v>
       </c>
       <c r="F6" s="6">
         <f>([3]Main!$J$7-[3]Main!$J$8)/FX!C5</f>
-        <v>-87849.921703726897</v>
+        <v>-87685.151609878085</v>
       </c>
       <c r="G6" s="6">
         <f>+E6-F6</f>
-        <v>1230464.3647881823</v>
+        <v>2372776.733609878</v>
       </c>
       <c r="H6" s="6">
         <f>+[3]Main!$J$4</f>
         <v>25931</v>
       </c>
-      <c r="I6" s="3" t="str">
-        <f>+I5</f>
+      <c r="I6" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J6" s="10">
+        <v>45652</v>
+      </c>
+      <c r="L6" s="20">
+        <f>($G6/$H6)/R6*5</f>
+        <v>43.040206847695082</v>
+      </c>
+      <c r="M6" s="21">
+        <f>($G6/$H6)/S6*5</f>
+        <v>29.290486478296977</v>
+      </c>
+      <c r="N6" s="21">
+        <f>($G6/$H6)/T6*5</f>
+        <v>23.378507858507859</v>
+      </c>
+      <c r="Q6" s="18">
+        <v>7.04</v>
+      </c>
+      <c r="R6">
+        <v>10.63</v>
+      </c>
+      <c r="S6">
+        <v>15.62</v>
+      </c>
+      <c r="T6">
+        <v>19.57</v>
+      </c>
+      <c r="Z6" s="13">
+        <f>17000000/NTD</f>
+        <v>520195.83843329252</v>
+      </c>
+      <c r="AA6" s="13"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2375</v>
+      </c>
+      <c r="E7" s="6">
+        <f>+D7*H7/FX!C2</f>
+        <v>1884520.3488372094</v>
+      </c>
+      <c r="F7" s="6">
+        <f>([3]Main!$J$7-[3]Main!$J$8)/FX!C5</f>
+        <v>-87685.151609878085</v>
+      </c>
+      <c r="G7" s="6">
+        <f>+E7-F7</f>
+        <v>1972205.5004470875</v>
+      </c>
+      <c r="H7" s="6">
+        <f>+[3]Main!$J$4</f>
+        <v>25931</v>
+      </c>
+      <c r="I7" s="3" t="str">
+        <f>+I6</f>
         <v>Q324</v>
       </c>
-      <c r="J6" s="10">
-        <f>+J5</f>
+      <c r="J7" s="10">
+        <f>+J6</f>
         <v>45652</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="Z7" s="13">
+        <f>+Z6</f>
+        <v>520195.83843329252</v>
+      </c>
+      <c r="AA7" s="13"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <v>394.27</v>
+      </c>
+      <c r="E8" s="6">
+        <f>+D8*H8</f>
+        <v>1927191.76</v>
+      </c>
+      <c r="F8" s="6">
+        <f>+[2]Main!$J$5-[2]Main!$J$6</f>
+        <v>-51883</v>
+      </c>
+      <c r="G8" s="6">
+        <f>+E8-F8</f>
+        <v>1979074.76</v>
+      </c>
+      <c r="H8" s="6">
+        <f>+[2]Main!$J$3</f>
+        <v>4888</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="10">
+        <v>45722</v>
+      </c>
+      <c r="L8" s="20">
+        <f>($G8/$H8)/R8</f>
+        <v>84.881417547615868</v>
+      </c>
+      <c r="M8" s="21">
+        <f>($G8/$H8)/S8</f>
+        <v>35.767169761672051</v>
+      </c>
+      <c r="N8" s="21">
+        <f>($G8/$H8)/T8</f>
+        <v>22.506079027355625</v>
+      </c>
+      <c r="O8" s="21"/>
+      <c r="Q8" s="18">
+        <v>1.23</v>
+      </c>
+      <c r="R8">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="S8">
+        <v>11.32</v>
+      </c>
+      <c r="T8">
+        <v>17.989999999999998</v>
+      </c>
+      <c r="Z8" s="13">
+        <v>1200000</v>
+      </c>
+      <c r="AA8" s="13">
+        <v>721000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="6">
-        <v>191600</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D9" s="6">
+        <v>199400</v>
+      </c>
+      <c r="E9" s="6">
         <f>1270340000/KRW</f>
         <v>875040.46840020665</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D10" s="4">
         <v>1348</v>
       </c>
-      <c r="E8" s="6">
-        <f>+D8*H8</f>
+      <c r="E10" s="6">
+        <f>+D10*H10</f>
         <v>530438</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F10" s="6">
         <f>+[4]Main!$L$5-[4]Main!$L$6</f>
         <v>1413.0000000000009</v>
       </c>
-      <c r="G8" s="6">
-        <f>+E8-F8</f>
+      <c r="G10" s="6">
+        <f>+E10-F10</f>
         <v>529025</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H10" s="6">
         <f>+[4]Main!$L$3</f>
         <v>393.5</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J10" s="10">
         <v>45581</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13">
+        <v>784000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
         <v>53</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C11" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="6">
-        <v>941000</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D11" s="6">
+        <v>1007000</v>
+      </c>
+      <c r="E11" s="6">
         <f>649720/KRW*1000</f>
         <v>447542.62097468576</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C12" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="3">
-        <v>383</v>
-      </c>
-      <c r="E10" s="6">
-        <f>+D10*H10</f>
-        <v>424686.22785799997</v>
-      </c>
-      <c r="F10" s="6">
-        <f>+[9]Main!$J$5-[9]Main!$J$6</f>
+      <c r="D12" s="4">
+        <v>587</v>
+      </c>
+      <c r="E12" s="6">
+        <f>+D12*H12</f>
+        <v>650889.85836199997</v>
+      </c>
+      <c r="F12" s="6">
+        <f>+[5]Main!$J$5-[5]Main!$J$6</f>
         <v>-4104</v>
       </c>
-      <c r="G10" s="6">
-        <f>+E10-F10</f>
-        <v>428790.22785799997</v>
-      </c>
-      <c r="H10" s="6">
-        <f>+[9]Main!$J$3</f>
+      <c r="G12" s="6">
+        <f>+E12-F12</f>
+        <v>654993.85836199997</v>
+      </c>
+      <c r="H12" s="6">
+        <f>+[5]Main!$J$3</f>
         <v>1108.841326</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J12" s="10">
         <v>45554</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="L12" s="20">
+        <f t="shared" ref="L12:N14" si="0">($G12/$H12)/R12</f>
+        <v>77.826239888750877</v>
+      </c>
+      <c r="M12" s="21">
+        <f t="shared" si="0"/>
+        <v>10.345029085037114</v>
+      </c>
+      <c r="N12" s="21">
+        <f t="shared" si="0"/>
+        <v>6.1756524909108119</v>
+      </c>
+      <c r="Q12" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="R12" s="2">
+        <v>7.59</v>
+      </c>
+      <c r="S12" s="2">
+        <v>57.1</v>
+      </c>
+      <c r="T12" s="2">
+        <v>95.65</v>
+      </c>
+      <c r="Z12" s="13">
+        <v>1446185</v>
+      </c>
+      <c r="AA12" s="13">
+        <v>749323</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="4">
-        <v>196.25</v>
-      </c>
-      <c r="E11" s="6">
-        <f>+D11*H11</f>
-        <v>322046.25</v>
-      </c>
-      <c r="F11" s="6">
-        <f>+[5]Main!$M$5-[5]Main!$M$6</f>
+      <c r="D13" s="4">
+        <v>200</v>
+      </c>
+      <c r="E13" s="6">
+        <f>+D13*H13</f>
+        <v>328200</v>
+      </c>
+      <c r="F13" s="6">
+        <f>+[6]Main!$M$5-[6]Main!$M$6</f>
         <v>4023</v>
       </c>
-      <c r="G11" s="6">
-        <f>+E11-F11</f>
-        <v>318023.25</v>
-      </c>
-      <c r="H11" s="6">
-        <f>+[5]Main!$M$3</f>
+      <c r="G13" s="6">
+        <f>+E13-F13</f>
+        <v>324177</v>
+      </c>
+      <c r="H13" s="6">
+        <f>+[6]Main!$M$3</f>
         <v>1641</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J13" s="10">
         <v>45939</v>
       </c>
-      <c r="K11">
+      <c r="K13">
         <v>1969</v>
       </c>
-      <c r="L11">
-        <v>3.84</v>
-      </c>
-      <c r="M11">
-        <v>6.14</v>
-      </c>
-      <c r="Q11" s="17">
-        <f>+$D11/L11</f>
-        <v>51.106770833333336</v>
-      </c>
-      <c r="R11" s="17">
-        <f>+$D11/M11</f>
-        <v>31.962540716612381</v>
-      </c>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="L13" s="20">
+        <f t="shared" si="0"/>
+        <v>74.546583422441444</v>
+      </c>
+      <c r="M13" s="21">
+        <f t="shared" si="0"/>
+        <v>28.839189207221875</v>
+      </c>
+      <c r="N13" s="21">
+        <f t="shared" si="0"/>
+        <v>17.606813375175562</v>
+      </c>
+      <c r="O13" s="21"/>
+      <c r="Q13" s="22">
+        <v>1</v>
+      </c>
+      <c r="R13" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="S13" s="2">
+        <v>6.85</v>
+      </c>
+      <c r="T13" s="2">
+        <v>11.22</v>
+      </c>
+      <c r="Z13" s="13">
+        <v>1291258</v>
+      </c>
+      <c r="AA13" s="13">
+        <v>820000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="3">
-        <v>337.09</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="D14" s="4">
+        <v>360</v>
+      </c>
+      <c r="E14" s="6">
         <v>267520</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="F14" s="6">
+        <f>+[7]Main!$K$5-[7]Main!$K$6</f>
+        <v>6926</v>
+      </c>
+      <c r="G14" s="6">
+        <f>+E14-F14</f>
+        <v>260594</v>
+      </c>
+      <c r="H14" s="6">
+        <f>+[7]Main!$K$3</f>
+        <v>799</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="L14" s="20">
+        <f t="shared" si="0"/>
+        <v>37.661684495920134</v>
+      </c>
+      <c r="M14" s="21">
+        <f t="shared" si="0"/>
+        <v>29.462528250647548</v>
+      </c>
+      <c r="N14" s="21">
+        <f t="shared" si="0"/>
+        <v>23.082108119934066</v>
+      </c>
+      <c r="Q14" s="18">
+        <v>8.61</v>
+      </c>
+      <c r="R14">
+        <v>8.66</v>
+      </c>
+      <c r="S14">
+        <v>11.07</v>
+      </c>
+      <c r="T14">
+        <v>14.13</v>
+      </c>
+      <c r="Z14" s="13">
+        <v>1030000</v>
+      </c>
+      <c r="AA14" s="13">
+        <v>665000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="3">
-        <v>208.87</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="D15" s="4">
+        <v>226</v>
+      </c>
+      <c r="E15" s="6">
         <v>260830</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="G15" s="6">
+        <f>E15-F15</f>
+        <v>260830</v>
+      </c>
+      <c r="J15" s="10">
+        <v>46089</v>
+      </c>
+      <c r="K15">
+        <v>1980</v>
+      </c>
+      <c r="W15" t="s">
+        <v>263</v>
+      </c>
+      <c r="X15" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>265</v>
+      </c>
+      <c r="Z15" s="13">
+        <v>1236539</v>
+      </c>
+      <c r="AA15" s="13">
+        <v>714596</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C16" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D16" s="4">
         <v>45.22</v>
       </c>
-      <c r="E14" s="6">
-        <f>+D14*H14</f>
+      <c r="E16" s="6">
+        <f>+D16*H16</f>
         <v>204891.82</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F16" s="6">
         <f>+[8]Main!$L$5-[8]Main!$L$6</f>
         <v>-6951</v>
       </c>
-      <c r="G14" s="6">
-        <f>+E14-F14</f>
+      <c r="G16" s="6">
+        <f>+E16-F16</f>
         <v>211842.82</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H16" s="6">
         <f>+[8]Main!$L$3</f>
         <v>4531</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J16" s="10">
         <v>45507</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="L16" s="20">
+        <f>($G16/$H16)/R16</f>
+        <v>-779.2349738836167</v>
+      </c>
+      <c r="M16" s="21">
+        <f>($G16/$H16)/S16</f>
+        <v>44.95586387790096</v>
+      </c>
+      <c r="N16" s="21">
+        <f>($G16/$H16)/T16</f>
+        <v>31.805509138106803</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>-4.38</v>
+      </c>
+      <c r="R16">
+        <v>-0.06</v>
+      </c>
+      <c r="S16">
+        <v>1.04</v>
+      </c>
+      <c r="T16">
+        <v>1.47</v>
+      </c>
+      <c r="Z16" s="13">
+        <v>1000000</v>
+      </c>
+      <c r="AA16" s="13">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C17" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="3">
-        <v>171.54</v>
-      </c>
-      <c r="E15" s="6">
-        <f>+D15*H15</f>
-        <v>191095.56</v>
-      </c>
-      <c r="F15" s="6">
-        <f>+[6]Main!$L$5-[6]Main!$L$6</f>
+      <c r="D17" s="4">
+        <v>132</v>
+      </c>
+      <c r="E17" s="6">
+        <f>+D17*H17</f>
+        <v>147048</v>
+      </c>
+      <c r="F17" s="6">
+        <f>+[9]Main!$L$5-[9]Main!$L$6</f>
         <v>-1522</v>
       </c>
-      <c r="G15" s="6">
-        <f>+E15-F15</f>
-        <v>192617.56</v>
-      </c>
-      <c r="H15" s="6">
-        <f>+[6]Main!$L$3</f>
+      <c r="G17" s="6">
+        <f>+E17-F17</f>
+        <v>148570</v>
+      </c>
+      <c r="H17" s="6">
+        <f>+[9]Main!$L$3</f>
         <v>1114</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J17" s="10">
         <v>45581</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="Z17" s="13">
+        <v>1350000</v>
+      </c>
+      <c r="AA17" s="13">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
         <v>57</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C18" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="4">
-        <v>1393</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="D18" s="4">
+        <v>1462</v>
+      </c>
+      <c r="E18" s="6">
         <v>182590</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="AA18" s="13">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
         <v>33</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C19" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="3">
-        <v>327.88</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="D19" s="4">
+        <v>310</v>
+      </c>
+      <c r="E19" s="6">
         <v>160070</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="AA19" s="13">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="3">
-        <v>196.78</v>
-      </c>
-      <c r="E18" s="6">
-        <f>+D18*H18</f>
-        <v>178591.96148736001</v>
-      </c>
-      <c r="F18" s="6">
-        <f>+[7]Main!$K$5-[7]Main!$K$6</f>
+      <c r="D20" s="4">
+        <v>190</v>
+      </c>
+      <c r="E20" s="6">
+        <f>+D20*H20</f>
+        <v>172438.62528000001</v>
+      </c>
+      <c r="F20" s="6">
+        <f>+[10]Main!$K$5-[10]Main!$K$6</f>
         <v>1153</v>
       </c>
-      <c r="G18" s="6">
-        <f>+E18-F18</f>
-        <v>177438.96148736001</v>
-      </c>
-      <c r="H18" s="6">
-        <f>+[7]Main!$K$3</f>
+      <c r="G20" s="6">
+        <f>+E20-F20</f>
+        <v>171285.62528000001</v>
+      </c>
+      <c r="H20" s="6">
+        <f>+[10]Main!$K$3</f>
         <v>907.57171200000005</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J20" s="10">
         <v>44946</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="AA20" s="13">
+        <v>830000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
         <v>118</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C21" t="s">
         <v>119</v>
       </c>
-      <c r="D19" s="3">
-        <v>119.15</v>
-      </c>
-      <c r="E19" s="6">
+      <c r="D21" s="4">
+        <v>133</v>
+      </c>
+      <c r="E21" s="6">
         <v>126470</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="AA21" s="13">
+        <v>1350000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
         <v>55</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D22" s="6">
         <v>41720</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E22" s="6">
         <f>124700</f>
         <v>124700</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
         <v>199</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C23" t="s">
         <v>200</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D23" s="6">
         <v>25535</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E23" s="6">
         <v>119990</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
         <v>79</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C24" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D24" s="4">
         <v>1775</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E24" s="6">
         <f>2830000/FX!$C$2</f>
         <v>86597.307221542229</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" t="s">
         <v>61</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C25" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D25" s="6">
         <v>6226</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E25" s="6">
         <v>73070</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
         <v>70</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D26" s="4">
         <v>209.6</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E26" s="6">
         <v>52970</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="AA26">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s">
         <v>81</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C27" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D27" s="3">
         <v>67.91</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E27" s="6">
         <v>36740</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="AA27">
+        <v>280918</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
         <v>47</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C28" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D28" s="3">
         <v>17.760000000000002</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E28" s="6">
         <f>134230/CNY</f>
         <v>19175.714285714286</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="1" t="s">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C29" t="s">
         <v>133</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D29" s="4">
         <v>20.65</v>
       </c>
-      <c r="E27" s="6">
-        <f>+D27*H27</f>
+      <c r="E29" s="6">
+        <f>+D29*H29</f>
         <v>13216</v>
       </c>
-      <c r="F27" s="6">
-        <f>+[10]Main!$M$5-[10]Main!$M$6</f>
+      <c r="F29" s="6">
+        <f>+[11]Main!$M$5-[11]Main!$M$6</f>
         <v>-504</v>
       </c>
-      <c r="G27" s="6">
-        <f>+E27-F27</f>
+      <c r="G29" s="6">
+        <f>+E29-F29</f>
         <v>13720</v>
       </c>
-      <c r="H27" s="6">
-        <f>+[10]Main!$M$3</f>
+      <c r="H29" s="6">
+        <f>+[11]Main!$M$3</f>
         <v>640</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J29" s="10">
         <v>45560</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" t="s">
         <v>201</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C30" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" t="s">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
         <v>207</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C31" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
         <v>83</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C32" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" t="s">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" t="s">
         <v>89</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C33" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" t="s">
         <v>209</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C34" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
         <v>93</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C35" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D35" s="3">
         <v>32.51</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E35" s="6">
         <v>28890</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" t="s">
         <v>211</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C36" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" t="s">
         <v>219</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C37" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A38" s="14"/>
+      <c r="B38" t="s">
+        <v>280</v>
+      </c>
+      <c r="C38" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s">
         <v>221</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C39" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s">
         <v>223</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C40" t="s">
         <v>224</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D40" s="4">
         <v>717</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E40" s="6">
         <v>41130</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" t="s">
         <v>239</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C41" t="s">
         <v>240</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D41" s="4">
         <v>353.5</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="14"/>
-      <c r="B39" t="s">
-        <v>257</v>
-      </c>
-      <c r="C39" t="s">
-        <v>256</v>
-      </c>
-      <c r="D39" s="4">
-        <v>3270</v>
-      </c>
-      <c r="E39" s="6">
-        <f>264920/FX!$C$5</f>
-        <v>8296.8994675853428</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" t="s">
-        <v>241</v>
-      </c>
-      <c r="C40" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="14"/>
-      <c r="B41" t="s">
-        <v>258</v>
-      </c>
-      <c r="C41" t="s">
-        <v>259</v>
-      </c>
-      <c r="D41" s="4">
-        <v>2355</v>
-      </c>
-      <c r="E41" s="6">
-        <f>315600/FX!$C$5</f>
-        <v>9884.1215158158466</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="14"/>
       <c r="B42" t="s">
+        <v>256</v>
+      </c>
+      <c r="C42" t="s">
+        <v>255</v>
+      </c>
+      <c r="D42" s="4">
+        <v>3270</v>
+      </c>
+      <c r="E42" s="6">
+        <f>264920/FX!$C$5</f>
+        <v>8281.337918099407</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>241</v>
+      </c>
+      <c r="C43" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A44" s="14"/>
+      <c r="B44" t="s">
+        <v>257</v>
+      </c>
+      <c r="C44" t="s">
+        <v>258</v>
+      </c>
+      <c r="D44" s="4">
+        <v>2355</v>
+      </c>
+      <c r="E44" s="6">
+        <f>315600/FX!$C$5</f>
+        <v>9865.5829946858394</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A45" s="14"/>
+      <c r="B45" t="s">
+        <v>259</v>
+      </c>
+      <c r="C45" t="s">
         <v>260</v>
       </c>
-      <c r="C42" t="s">
-        <v>261</v>
-      </c>
-      <c r="D42" s="4">
+      <c r="D45" s="4">
         <v>159</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E45" s="6">
         <f>41430/FX!$C$5</f>
-        <v>1297.5258377701221</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" t="s">
+        <v>1295.0922163175994</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
         <v>99</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C46" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D46" s="4">
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
         <v>105</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C47" t="s">
         <v>106</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D47" s="3">
         <v>47.15</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E47" s="6">
         <v>26330</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
         <v>109</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C48" t="s">
         <v>110</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D48" s="3">
         <v>60.46</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E48" s="6">
         <v>23800</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" t="s">
-        <v>248</v>
-      </c>
-      <c r="C46" t="s">
-        <v>249</v>
-      </c>
-      <c r="D46" s="3">
-        <v>118.63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" s="4">
-        <v>61.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C48" t="s">
-        <v>135</v>
-      </c>
-      <c r="D48" s="4">
-        <v>112</v>
-      </c>
-      <c r="E48" s="6">
-        <f>+D48*H48</f>
-        <v>15167.281808</v>
-      </c>
-      <c r="F48" s="6">
-        <f>+[11]Main!$J$5-[11]Main!$J$6</f>
-        <v>446.97199999999998</v>
-      </c>
-      <c r="G48" s="6">
-        <f>+E48-F48</f>
-        <v>14720.309808</v>
-      </c>
-      <c r="H48" s="6">
-        <f>+[11]Main!$J$3</f>
-        <v>135.42215899999999</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J48" s="10">
-        <v>45561</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="AA48">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>136</v>
+        <v>269</v>
       </c>
       <c r="C49" t="s">
-        <v>137</v>
+        <v>270</v>
       </c>
       <c r="D49" s="4">
-        <v>13</v>
+        <v>1222</v>
       </c>
       <c r="E49" s="6">
         <f>+D49*H49</f>
-        <v>10543.625651</v>
+        <v>180965.68427599999</v>
       </c>
       <c r="F49" s="6">
-        <f>+[12]Main!$K$5-[12]Main!$K$6</f>
-        <v>1203</v>
+        <f>+[12]Main!$L$5-[12]Main!$L$6</f>
+        <v>3735</v>
       </c>
       <c r="G49" s="6">
         <f>+E49-F49</f>
+        <v>177230.68427599999</v>
+      </c>
+      <c r="H49" s="6">
+        <f>+[12]Main!$L$3</f>
+        <v>148.08975799999999</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J49" s="10">
+        <v>46146</v>
+      </c>
+      <c r="AA49">
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" t="s">
+        <v>248</v>
+      </c>
+      <c r="C50" t="s">
+        <v>249</v>
+      </c>
+      <c r="D50" s="3">
+        <v>118.63</v>
+      </c>
+      <c r="AA50">
+        <v>615000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="4">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C52" t="s">
+        <v>135</v>
+      </c>
+      <c r="D52" s="4">
+        <v>112</v>
+      </c>
+      <c r="E52" s="6">
+        <f>+D52*H52</f>
+        <v>15167.281808</v>
+      </c>
+      <c r="F52" s="6">
+        <f>+[13]Main!$J$5-[13]Main!$J$6</f>
+        <v>446.97199999999998</v>
+      </c>
+      <c r="G52" s="6">
+        <f>+E52-F52</f>
+        <v>14720.309808</v>
+      </c>
+      <c r="H52" s="6">
+        <f>+[13]Main!$J$3</f>
+        <v>135.42215899999999</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J52" s="10">
+        <v>45561</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C53" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="4">
+        <v>13</v>
+      </c>
+      <c r="E53" s="6">
+        <f>+D53*H53</f>
+        <v>10543.625651</v>
+      </c>
+      <c r="F53" s="6">
+        <f>+[14]Main!$K$5-[14]Main!$K$6</f>
+        <v>1203</v>
+      </c>
+      <c r="G53" s="6">
+        <f>+E53-F53</f>
         <v>9340.6256510000003</v>
       </c>
-      <c r="H49" s="6">
-        <f>+[12]Main!$K$3</f>
+      <c r="H53" s="6">
+        <f>+[14]Main!$K$3</f>
         <v>811.04812700000002</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I53" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J53" s="10">
         <v>45561</v>
       </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="1" t="s">
+      <c r="AA53">
+        <v>752335</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C54" t="s">
         <v>244</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D54" s="4">
         <v>23.19</v>
       </c>
-      <c r="E50" s="6">
-        <f>+D50*H50</f>
+      <c r="E54" s="6">
+        <f>+D54*H54</f>
         <v>1481.01784776</v>
       </c>
-      <c r="F50" s="6">
-        <f>+[13]Main!$J$5-[13]Main!$J$6</f>
+      <c r="F54" s="6">
+        <f>+[15]Main!$J$5-[15]Main!$J$6</f>
         <v>295.214</v>
       </c>
-      <c r="G50" s="6">
-        <f>+E50-F50</f>
+      <c r="G54" s="6">
+        <f>+E54-F54</f>
         <v>1185.8038477600001</v>
       </c>
-      <c r="H50" s="6">
-        <f>+[13]Main!$J$3</f>
+      <c r="H54" s="6">
+        <f>+[15]Main!$J$3</f>
         <v>63.864503999999997</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I54" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="J50" s="10">
+      <c r="J54" s="10">
         <v>45796</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
         <v>108</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="L3:P3"/>
+    <mergeCell ref="Q3:V3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{82B60337-F6F7-4A89-BE21-94E4E4FAE923}"/>
-    <hyperlink ref="B18" r:id="rId2" xr:uid="{89BFBE39-15FE-4D88-BD35-419556A195F8}"/>
-    <hyperlink ref="B14" r:id="rId3" xr:uid="{ACBF0F19-D83E-41D4-B3AD-01439A0CCE2D}"/>
-    <hyperlink ref="B11" r:id="rId4" xr:uid="{0B4AADBB-7802-4155-9477-7B8867856D77}"/>
-    <hyperlink ref="B5" r:id="rId5" xr:uid="{D5C26AF1-ADC4-4E03-9D8B-12F3C24C324B}"/>
-    <hyperlink ref="B6" r:id="rId6" xr:uid="{DD4F0CC9-D485-4053-9B41-DE6F39511946}"/>
-    <hyperlink ref="B4" r:id="rId7" xr:uid="{05815C98-BE17-4CF3-942D-C5BFAB80DA80}"/>
-    <hyperlink ref="B10" r:id="rId8" xr:uid="{37FE970B-81E9-4AF7-98E1-474982CC16D7}"/>
-    <hyperlink ref="B27" r:id="rId9" xr:uid="{CF0C3BE9-553F-4E6A-8F72-3B6D86F868FC}"/>
-    <hyperlink ref="B48" r:id="rId10" xr:uid="{35D78F35-BD1B-401F-9830-193EF147D21A}"/>
-    <hyperlink ref="B49" r:id="rId11" xr:uid="{8FC74BE2-2095-4EFE-8F49-C1E00A6EF2C6}"/>
-    <hyperlink ref="B15" r:id="rId12" xr:uid="{E7CBB7C3-B2DF-42D5-A84A-8A1B7E26DDB6}"/>
-    <hyperlink ref="B8" r:id="rId13" xr:uid="{3EEE25FB-8581-4AA9-ADEF-37DC0B2F3F4D}"/>
-    <hyperlink ref="B50" r:id="rId14" xr:uid="{3A48277A-E40F-4BB9-B4C3-9290548C0B09}"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{82B60337-F6F7-4A89-BE21-94E4E4FAE923}"/>
+    <hyperlink ref="B20" r:id="rId2" xr:uid="{89BFBE39-15FE-4D88-BD35-419556A195F8}"/>
+    <hyperlink ref="B16" r:id="rId3" xr:uid="{ACBF0F19-D83E-41D4-B3AD-01439A0CCE2D}"/>
+    <hyperlink ref="B13" r:id="rId4" xr:uid="{0B4AADBB-7802-4155-9477-7B8867856D77}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{D5C26AF1-ADC4-4E03-9D8B-12F3C24C324B}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{DD4F0CC9-D485-4053-9B41-DE6F39511946}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{05815C98-BE17-4CF3-942D-C5BFAB80DA80}"/>
+    <hyperlink ref="B12" r:id="rId8" xr:uid="{37FE970B-81E9-4AF7-98E1-474982CC16D7}"/>
+    <hyperlink ref="B29" r:id="rId9" xr:uid="{CF0C3BE9-553F-4E6A-8F72-3B6D86F868FC}"/>
+    <hyperlink ref="B52" r:id="rId10" xr:uid="{35D78F35-BD1B-401F-9830-193EF147D21A}"/>
+    <hyperlink ref="B53" r:id="rId11" xr:uid="{8FC74BE2-2095-4EFE-8F49-C1E00A6EF2C6}"/>
+    <hyperlink ref="B17" r:id="rId12" xr:uid="{E7CBB7C3-B2DF-42D5-A84A-8A1B7E26DDB6}"/>
+    <hyperlink ref="B10" r:id="rId13" xr:uid="{3EEE25FB-8581-4AA9-ADEF-37DC0B2F3F4D}"/>
+    <hyperlink ref="B54" r:id="rId14" xr:uid="{3A48277A-E40F-4BB9-B4C3-9290548C0B09}"/>
+    <hyperlink ref="B15" r:id="rId15" xr:uid="{0E1B41B2-39E3-482E-80B4-4D069EE9643C}"/>
+    <hyperlink ref="B14" r:id="rId16" xr:uid="{5BA02E53-CE6F-4CB1-A08A-138D1B40007E}"/>
+    <hyperlink ref="B49" r:id="rId17" xr:uid="{336EFAF6-6C79-4F1F-A0B5-C64D94F56B90}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3246,23 +3822,23 @@
         <v>123</v>
       </c>
       <c r="D5" s="2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E5" s="13">
         <f>+D5*H5</f>
-        <v>11336.946911999999</v>
+        <v>17711.180015999998</v>
       </c>
       <c r="F5" s="13">
-        <f>+[14]Main!$J$5-[14]Main!$J$6</f>
-        <v>1657</v>
+        <f>+[16]Main!$J$5-[16]Main!$J$6</f>
+        <v>3336.799</v>
       </c>
       <c r="G5" s="13">
         <f>+E5-F5</f>
-        <v>9679.9469119999994</v>
+        <v>14374.381015999999</v>
       </c>
       <c r="H5" s="13">
-        <f>+[14]Main!$J$3</f>
-        <v>354.27959099999998</v>
+        <f>+[16]Main!$J$3</f>
+        <v>368.98291699999999</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>192</v>
@@ -3279,22 +3855,22 @@
         <v>126</v>
       </c>
       <c r="D6">
-        <v>7.95</v>
+        <v>14.95</v>
       </c>
       <c r="E6" s="13">
         <f>+D6*H6</f>
-        <v>2254.1976244500001</v>
+        <v>4239.0257214499998</v>
       </c>
       <c r="F6" s="13">
-        <f>+[15]Main!$L$5-[15]Main!$L$6</f>
+        <f>+[17]Main!$L$5-[17]Main!$L$6</f>
         <v>217</v>
       </c>
       <c r="G6" s="13">
         <f>E6-F6</f>
-        <v>2037.1976244500001</v>
+        <v>4022.0257214499998</v>
       </c>
       <c r="H6" s="13">
-        <f>+[15]Main!$L$3</f>
+        <f>+[17]Main!$L$3</f>
         <v>283.54687100000001</v>
       </c>
       <c r="I6" s="3" t="s">
@@ -3312,7 +3888,7 @@
         <v>140</v>
       </c>
       <c r="D7" s="2">
-        <v>18</v>
+        <v>7.15</v>
       </c>
       <c r="E7" s="13">
         <v>2000</v>
@@ -3326,22 +3902,22 @@
         <v>124</v>
       </c>
       <c r="D8" s="2">
-        <v>6.45</v>
+        <v>15.75</v>
       </c>
       <c r="E8" s="13">
         <f>+D8*H8</f>
-        <v>2236.3348474499999</v>
+        <v>5460.8176507499993</v>
       </c>
       <c r="F8" s="13">
-        <f>+[16]Main!$L$5-[16]Main!$L$6</f>
+        <f>+[18]Main!$L$5-[18]Main!$L$6</f>
         <v>804.03300000000002</v>
       </c>
       <c r="G8" s="13">
         <f>+E8-F8</f>
-        <v>1432.30184745</v>
+        <v>4656.7846507499989</v>
       </c>
       <c r="H8" s="13">
-        <f>+[16]Main!$L$3</f>
+        <f>+[18]Main!$L$3</f>
         <v>346.71858099999997</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -3359,7 +3935,18 @@
         <v>195</v>
       </c>
       <c r="D9" s="2">
-        <v>5</v>
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" s="2">
+        <v>8.93</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -3612,7 +4199,7 @@
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3856,7 +4443,7 @@
         <v>3071963.48</v>
       </c>
       <c r="F3" s="6">
-        <f>+[17]Main!$O$5-[17]Main!$O$6</f>
+        <f>+[19]Main!$O$5-[19]Main!$O$6</f>
         <v>31288</v>
       </c>
       <c r="G3" s="6">
@@ -3864,7 +4451,7 @@
         <v>3040675.48</v>
       </c>
       <c r="H3" s="6">
-        <f>+[17]Main!$O$3</f>
+        <f>+[19]Main!$O$3</f>
         <v>14948</v>
       </c>
       <c r="I3" s="3" t="s">
@@ -3874,7 +4461,7 @@
         <v>45750</v>
       </c>
       <c r="K3" s="2">
-        <f>[17]Model!$CE$39</f>
+        <f>[19]Model!$CE$39</f>
         <v>0.46906012207980208</v>
       </c>
       <c r="L3" s="7">
@@ -3882,11 +4469,11 @@
         <v>-0.99771758005897615</v>
       </c>
       <c r="M3" s="8">
-        <f>+[17]Model!$CE$36</f>
+        <f>+[19]Model!$CE$36</f>
         <v>4.1953407917453944E-2</v>
       </c>
       <c r="N3" s="8">
-        <f>+[17]Model!$CE$37</f>
+        <f>+[19]Model!$CE$37</f>
         <v>3.632000000000013E-2</v>
       </c>
       <c r="O3" s="8">
@@ -3914,7 +4501,7 @@
         <v>268168.58880661271</v>
       </c>
       <c r="F4" s="6">
-        <f>([18]Main!$K$5-[18]Main!$K$6)/KRW</f>
+        <f>([20]Main!$K$5-[20]Main!$K$6)/KRW</f>
         <v>64.28214224212158</v>
       </c>
       <c r="G4" s="6">
@@ -3922,7 +4509,7 @@
         <v>268104.30666437058</v>
       </c>
       <c r="H4" s="6">
-        <f>+[18]Main!$K$3</f>
+        <f>+[20]Main!$K$3</f>
         <v>6758.9192499999999</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -4216,19 +4803,19 @@
       </c>
       <c r="E29" s="6">
         <f>+D29*H29</f>
-        <v>13816.904048999999</v>
+        <v>14390.333762999999</v>
       </c>
       <c r="F29" s="6">
-        <f>+[14]Main!$J$5-[14]Main!$J$6</f>
-        <v>1657</v>
+        <f>+[16]Main!$J$5-[16]Main!$J$6</f>
+        <v>3336.799</v>
       </c>
       <c r="G29" s="6">
         <f>+E29-F29</f>
-        <v>12159.904048999999</v>
+        <v>11053.534763</v>
       </c>
       <c r="H29" s="6">
-        <f>+[14]Main!$J$3</f>
-        <v>354.27959099999998</v>
+        <f>+[16]Main!$J$3</f>
+        <v>368.98291699999999</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>128</v>
@@ -4252,7 +4839,7 @@
         <v>2412.9838722099998</v>
       </c>
       <c r="F30" s="6">
-        <f>+[15]Main!$L$5-[15]Main!$L$6</f>
+        <f>+[17]Main!$L$5-[17]Main!$L$6</f>
         <v>217</v>
       </c>
       <c r="G30" s="6">
@@ -4260,7 +4847,7 @@
         <v>2195.9838722099998</v>
       </c>
       <c r="H30" s="6">
-        <f>+[15]Main!$L$3</f>
+        <f>+[17]Main!$L$3</f>
         <v>283.54687100000001</v>
       </c>
       <c r="I30" s="3" t="s">
@@ -4312,7 +4899,7 @@
         <v>28641.902146</v>
       </c>
       <c r="F34" s="6">
-        <f>+[19]Main!$I$5-[19]Main!$I$6</f>
+        <f>+[21]Main!$I$5-[21]Main!$I$6</f>
         <v>-373.40000000000003</v>
       </c>
       <c r="G34" s="6">
@@ -4320,7 +4907,7 @@
         <v>29015.302146000002</v>
       </c>
       <c r="H34" s="6">
-        <f>+[19]Main!$I$3</f>
+        <f>+[21]Main!$I$3</f>
         <v>115.959118</v>
       </c>
       <c r="I34" s="3" t="s">
@@ -4374,7 +4961,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC72FDEE-60E0-4B9B-AACF-AB184FD947A1}">
-  <dimension ref="B2:C6"/>
+  <dimension ref="B2:C7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.1796875" customWidth="1"/>
@@ -4406,18 +4993,23 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C5">
-        <v>31.93</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C6">
         <v>157.66</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
